--- a/results/correlation/.counts/counts_correct.xlsx
+++ b/results/correlation/.counts/counts_correct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Clustering-Validity\results\correlation\.counts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CF26DD-8604-4CC1-9145-7E0BEF8F3B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB81484D-B516-4420-8FFD-2F451217A024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92E53E66-B5D4-4295-B5F2-92D11FF46DE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{92E53E66-B5D4-4295-B5F2-92D11FF46DE1}"/>
   </bookViews>
   <sheets>
     <sheet name="counts_correct" sheetId="1" r:id="rId1"/>
@@ -1044,9 +1044,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D23473FF-7349-4627-9B00-61A36C054E9A}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>46</v>
       </c>
